--- a/data/osnovi_ai.xlsx
+++ b/data/osnovi_ai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coding\WibeCode Projects\rus_tuit_quizzer_claude\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DownloadsPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6670CED-F66A-4415-B119-4A1F5795E47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6DC8A2-CE8E-4619-A96E-4C9D05A2744A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1267">
   <si>
     <t>id</t>
   </si>
@@ -3831,6 +3831,9 @@
   </si>
   <si>
     <t>q235</t>
+  </si>
+  <si>
+    <t>Данные → Информация → Знание</t>
   </si>
 </sst>
 </file>
@@ -5009,7 +5012,7 @@
         <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>159</v>
+        <v>1266</v>
       </c>
       <c r="D35" t="s">
         <v>160</v>
